--- a/human_validation/judge/kor/judge_D018_S003_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D018_S003_P003__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,124 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 스미스 선생님입니다. 먼저, 오늘 저를 찾아오시게 된 이유를 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 결국 진료를 받기로 결심하게 만든 건, 예전에 저를 균형 잡아주던 것들에 더 이상 관심이 안 간다는 거였어요. 요트 경주, 토요일마다 하던 역사 협회 봉사, 심지어 목공 작업까지도요. 이제는 다 귀찮은 일처럼 느껴져서 계속 미루게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 요트 경주와 역사 협회, 목공 작업에 대한 이 흥미 상실을 얼마나 오래 느끼셨나요? 며칠, 몇 주, 아니면 그보다 더 오래됐나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 사업 구조조정 중에 있었던 비계 사고 이후부터예요 — 그러니까, 이제 1년이 좀 넘었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 1년 전쯤 사고 이후로, 이런 식으로 기분이 가라앉고 처지는 게 거의 매일 큰 변화 없이 계속되고 있나요, 아니면 몇 주씩 거의 평소 상태로 돌아온 기간도 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 꽤 계속돼요. 항상 정확히 슬픔은 아니지만, 이 낮은 수준의 불안감과 죄책감이 저를 따라다녀요. 제가 위험 요소를 하나 더 봤어야 했다는 생각이 계속 들어요, 다들 안전 관리가 다 되어 있었다고 말해도요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 사고 이후로, 비계 사고 자체에 대한 침투적인 기억이나 플래시백, 괴로운 꿈을 경험하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네. 예상치 못하게 찾아와요 — 비계가 떨어지는 게 사진처럼 선명하게 머릿속에 보여요. 금속이 부딪히는 소리나 후진 경고음이 그걸 촉발할 수 있어요. 그러면 몇 분 동안 지금 하고 있는 회의나 대화에 집중하기가 힘들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 비계 사고를 떠올리게 하는 장소나 활동, 대화를 적극적으로 피하시는 걸 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네. 그 해안가 현장이나 크레인 근처의 항구 산책로에 안 가도 되게 하루 일정을 짜는 데 꽤 익숙해졌어요. 그리고 누가 뭐가 잘못됐는지 얘기하기 시작하면, 보통 어떻게든 그 대화에서 빠져나갈 방법을 찾아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>진단명: 외상후 스트레스장애 (D018)
 인구통계: 성별 남성 / 나이 51 / 직업상태 project management specialist / 최종학력 학사
@@ -575,191 +684,45 @@
 증상 지속 기간: 1 year and 1 months
 추가 요건: 
 주호소 증상 코드: S025
-배경 서술: 로이의 회사에서 대규모 사업 구조조정이 진행되는 동안, 그는 지연된 해안가 건설 프로젝트를 안정화하는 업무에 배정되었고, 현장 점검 중 자신이 평소 자부심을 가지고 예측하던 위험 관리 조치들이 있었음에도 불구하고 도급업체 직원이 심각하게 다치는 비계 붕괴 사고를 목격했다. 그 후 1년 1개월 동안, 그는 계속 기능은 유지했지만 프로젝트 현장과 특정 항구 산책로, 건설 소음을 피하는 방향으로 점점 더 삶을 제한했고, 그동안 그의 일상을 지탱해주던 요트 경주, 역사 협회 봉사, 정원 가꾸기, 목공 작업에 대한 흥미를 잃어갔다. 그는 잠을 잘 자지 못했고, 반복적으로 원치 않는 기억이 떠올랐으며, 사고 과정의 핵심 부분을 설명할 수 없었고, 지속적인 불안감과 죄책감 속에서 지냈으며, 가족이나 취미에서 만족감을 느끼기 힘들어했고, 갑작스러운 금속성 소음에 심하게 놀랐으며, 예전 같으면 피했을 날씨에도 몇 차례 안전하지 않은 단독 보트 운행을 했다. 로이는 스트레스로 인한 피로 때문에 방문한 1차 진료에서 이런 변화들을 언급한 후 정신과 진료를 받게 되었고, 이 패턴이 프로젝트 리더십을 저해하기 시작할까 봐 두려워서 의뢰를 받아들였다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 스미스 선생님입니다. 먼저, 오늘 저를 찾아오시게 된 이유를 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 결국 진료를 받기로 결심하게 만든 건, 예전에 저를 균형 잡아주던 것들에 더 이상 관심이 안 간다는 거였어요. 요트 경주, 토요일마다 하던 역사 협회 봉사, 심지어 목공 작업까지도요. 이제는 다 귀찮은 일처럼 느껴져서 계속 미루게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 요트 경주와 역사 협회, 목공 작업에 대한 이 흥미 상실을 얼마나 오래 느끼셨나요? 며칠, 몇 주, 아니면 그보다 더 오래됐나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 사업 구조조정 중에 있었던 비계 사고 이후부터예요 — 그러니까, 이제 1년이 좀 넘었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 1년 전쯤 사고 이후로, 이런 식으로 기분이 가라앉고 처지는 게 거의 매일 큰 변화 없이 계속되고 있나요, 아니면 몇 주씩 거의 평소 상태로 돌아온 기간도 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 꽤 계속돼요. 항상 정확히 슬픔은 아니지만, 이 낮은 수준의 불안감과 죄책감이 저를 따라다녀요. 제가 위험 요소를 하나 더 봤어야 했다는 생각이 계속 들어요, 다들 안전 관리가 다 되어 있었다고 말해도요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 사고 이후로, 비계 사고 자체에 대한 침투적인 기억이나 플래시백, 괴로운 꿈을 경험하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네. 예상치 못하게 찾아와요 — 비계가 떨어지는 게 사진처럼 선명하게 머릿속에 보여요. 금속이 부딪히는 소리나 후진 경고음이 그걸 촉발할 수 있어요. 그러면 몇 분 동안 지금 하고 있는 회의나 대화에 집중하기가 힘들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 비계 사고를 떠올리게 하는 장소나 활동, 대화를 적극적으로 피하시는 걸 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네. 그 해안가 현장이나 크레인 근처의 항구 산책로에 안 가도 되게 하루 일정을 짜는 데 꽤 익숙해졌어요. 그리고 누가 뭐가 잘못됐는지 얘기하기 시작하면, 보통 어떻게든 그 대화에서 빠져나갈 방법을 찾아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
+배경 서술: 로이의 회사에서 대규모 사업 구조조정이 진행되는 동안, 그는 지연된 해안가 건설 프로젝트를 안정화하는 업무에 배정되었고, 현장 점검 중 자신이 평소 자부심을 가지고 예측하던 위험 관리 조치들이 있었음에도 불구하고 도급업체 직원이 심각하게 다치는 비계 붕괴 사고를 목격했다. 그 후 1년 1개월 동안, 그는 계속 기능은 유지했지만 프로젝트 현장과 특정 항구 산책로, 건설 소음을 피하는 방향으로 점점 더 삶을 제한했고, 그동안 그의 일상을 지탱해주던 요트 경주, 역사 협회 봉사, 정원 가꾸기, 목공 작업에 대한 흥미를 잃어갔다. 그는 잠을 잘 자지 못했고, 반복적으로 원치 않는 기억이 떠올랐으며, 사고 과정의 핵심 부분을 설명할 수 없었고, 지속적인 불안감과 죄책감 속에서 지냈으며, 가족이나 취미에서 만족감을 느끼기 힘들어했고, 갑작스러운 금속성 소음에 심하게 놀랐으며, 예전 같으면 피했을 날씨에도 몇 차례 안전하지 않은 단독 보트 운행을 했다. 로이는 스트레스로 인한 피로 때문에 방문한 1차 진료에서 이런 변화들을 언급한 후 정신과 진료를 받게 되었고, 이 패턴이 프로젝트 리더십을 저해하기 시작할까 봐 두려워서 의뢰를 받아들였다.
+표집된 증상 목록:
+  - S025 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S069 침투 증상: 외상 사건에 대한 반복적이고 비자발적이며 침투적인 고통스러운 기억.
+  - S070 외상 관련 회피: 외상 사건과 관련된 자극을 지속적으로 회피함.
+  - S071 외상 관련 기억상실: 외상 사건의 중요한 부분을 기억하지 못함(통상 해리성 기억상실에 의한 것으로, 두부 손상이나 알코올 등 다른 요인에 의한 것이 아님).
+  - S074 지속적인 부정적 정서 상태: 지속적인 부정적 정서 상태(예: 두려움, 공포, 분노, 죄책감, 수치심).
+  - S076 긍정적 정서 표현 불능: 긍정적 정서를 지속적으로 경험하지 못함(예: 행복, 만족, 애정을 느끼지 못함).
+  - S078 무모/자기파괴적 행동: 자신의 안전이나 건강을 위태롭게 하는 무모하거나 자기파괴적인 행동 양상.
+  - S080 과장된 놀람 반응: 사소한 자극에도 과장되게 놀라는 반응.</t>
+        </is>
+      </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 외상후 스트레스장애 (D018, ICD: F43.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: trauma_related_symptoms (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 침투 증상: 외상 사건에 대한 반복적이고 비자발적이며 침투적인 고통스러운 기억.; 외상 관련 회피: 외상 사건과 관련된 자극을 지속적으로 회피함.
-  누락: (없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: trauma_related_alterations (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 지속적인 부정적 정서 상태: 지속적인 부정적 정서 상태(예: 두려움, 공포, 분노, 죄책감, 수치심).
-  누락: 외상 관련 기억상실: 외상 사건의 중요한 부분을 기억하지 못함(통상 해리성 기억상실에 의한 것으로, 두부 손상이나 알코올 등 다른 요인에 의한 것이 아님).; 부정적 신념: 자신, 타인, 세상에 대한 지속적이고 과장된 부정적 믿음이나 기대.; 왜곡된 인지와 비난: 외상 사건의 원인이나 결과에 대해 지속적이고 왜곡된 인지를 가지고 있어 자신이나 타인을 비난하게 됨.; 사회적 유리감: 타인으로부터 동떨어지거나 소외된 느낌.; 긍정적 정서 표현 불능: 긍정적 정서를 지속적으로 경험하지 못함(예: 행복, 만족, 애정을 느끼지 못함).</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: arousal_and_reactivity (관계=must_include, 요구개수=2, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 과민성/공격성: 사소하거나 별다른 도발 없이도 언어적·신체적 공격성으로 나타나는 과민한 행동과 분노 폭발.; 무모/자기파괴적 행동: 자신의 안전이나 건강을 위태롭게 하는 무모하거나 자기파괴적인 행동 양상.; 과각성: 주변 환경에 대해 지속적으로 경계하고 긴장하는 상태.; 과장된 놀람 반응: 사소한 자극에도 과장되게 놀라는 반응.</t>
+          <t>의사의 최종 진단: 외상후 스트레스장애 (D018, ICD: F43.1)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: trauma_related_symptoms (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 침투 증상: 외상 사건에 대한 반복적이고 비자발적이며 침투적인 고통스러운 기억.
+  - 외상 관련 회피: 외상 사건과 관련된 자극을 지속적으로 회피함.
+체크리스트 그룹: trauma_related_alterations (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - 지속적인 부정적 정서 상태: 지속적인 부정적 정서 상태(예: 두려움, 공포, 분노, 죄책감, 수치심).
+체크리스트 그룹: arousal_and_reactivity (관계=must_include, 요구개수=2, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D018_S003_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D018_S003_P003__claude-sonnet-5_kor.xlsx
@@ -670,6 +670,11 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -718,11 +723,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D018_S003_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D018_S003_P003__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.1471</v>
+        <v>0.2155</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.1667</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.9167</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
